--- a/formlar/4. Dikimhane Bölümü/EMS.QA.FRM.03.05. QA_Baskı Nakış Onay Formu.xlsx
+++ b/formlar/4. Dikimhane Bölümü/EMS.QA.FRM.03.05. QA_Baskı Nakış Onay Formu.xlsx
@@ -4897,8 +4897,10 @@
       <c r="AN2" s="87"/>
       <c r="AO2" s="87"/>
       <c r="AP2" s="87"/>
-      <c r="AQ2" s="24" t="s">
-        <v>46</v>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>EMS.QA.FRM.03.05</t>
+        </is>
       </c>
       <c r="AR2" s="24"/>
       <c r="AS2" s="24"/>
@@ -6704,8 +6706,10 @@
       <c r="AN2" s="23"/>
       <c r="AO2" s="23"/>
       <c r="AP2" s="23"/>
-      <c r="AQ2" s="24" t="s">
-        <v>46</v>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>EMS.QA.FRM.03.05</t>
+        </is>
       </c>
       <c r="AR2" s="24"/>
       <c r="AS2" s="24"/>
